--- a/resource/groundTruths/architecture/CF_M09_ground_truth_architecture.xlsx
+++ b/resource/groundTruths/architecture/CF_M09_ground_truth_architecture.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/architecture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3852F6FD-1CEA-6642-A09E-B9C1571ACB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31BEFD8E-38B6-974A-8941-03CB59570951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16720" yWindow="900" windowWidth="12520" windowHeight="16600" xr2:uid="{5C48AE06-3142-BB44-8E2A-9AD236D99D27}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="153">
   <si>
     <t>Document ID</t>
   </si>
@@ -492,6 +492,9 @@
   </si>
   <si>
     <t>The data layer is divided into several AWS services that allow for improved system performance and scalability.</t>
+  </si>
+  <si>
+    <t>Fixed Type</t>
   </si>
 </sst>
 </file>
@@ -883,10 +886,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8BB644F-E3FB-9344-8618-EE146D2A8012}">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="28" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -908,8 +911,11 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -932,7 +938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -955,7 +961,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -975,7 +981,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -995,7 +1001,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1018,7 +1024,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1041,7 +1047,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1061,7 +1067,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1084,7 +1090,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -1107,7 +1113,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -1130,7 +1136,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1153,7 +1159,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1176,7 +1182,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1199,7 +1205,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1222,7 +1228,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>7</v>
       </c>

--- a/resource/groundTruths/architecture/CF_M09_ground_truth_architecture.xlsx
+++ b/resource/groundTruths/architecture/CF_M09_ground_truth_architecture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/architecture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31BEFD8E-38B6-974A-8941-03CB59570951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{089907FA-E1ED-914C-94E9-71344290D693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16720" yWindow="900" windowWidth="12520" windowHeight="16600" xr2:uid="{5C48AE06-3142-BB44-8E2A-9AD236D99D27}"/>
+    <workbookView xWindow="37980" yWindow="1440" windowWidth="12520" windowHeight="16600" xr2:uid="{5C48AE06-3142-BB44-8E2A-9AD236D99D27}"/>
   </bookViews>
   <sheets>
     <sheet name="Architectural Units" sheetId="2" r:id="rId1"/>
@@ -182,9 +182,6 @@
     <t>React</t>
   </si>
   <si>
-    <t>Nest</t>
-  </si>
-  <si>
     <t>Within the software engineering specialization, this project focuses on web technologies, specifically using React [2] and Nest [3] for the codebase and AWS cloud services [4] for the infrastructure.</t>
   </si>
   <si>
@@ -495,6 +492,9 @@
   </si>
   <si>
     <t>Fixed Type</t>
+  </si>
+  <si>
+    <t>NestJS</t>
   </si>
 </sst>
 </file>
@@ -912,7 +912,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -929,10 +929,10 @@
         <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G2">
         <v>9</v>
@@ -949,13 +949,13 @@
         <v>46</v>
       </c>
       <c r="D3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E3" t="s">
         <v>48</v>
       </c>
-      <c r="E3" t="s">
-        <v>49</v>
-      </c>
       <c r="F3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G3">
         <v>9</v>
@@ -969,13 +969,13 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G4">
         <v>9</v>
@@ -989,13 +989,13 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" t="s">
         <v>52</v>
-      </c>
-      <c r="E5" t="s">
-        <v>53</v>
       </c>
       <c r="G5">
         <v>9</v>
@@ -1009,13 +1009,13 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" t="s">
         <v>57</v>
-      </c>
-      <c r="D6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" t="s">
-        <v>58</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
@@ -1032,13 +1032,13 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" t="s">
         <v>62</v>
-      </c>
-      <c r="E7" t="s">
-        <v>63</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
@@ -1055,13 +1055,13 @@
         <v>23</v>
       </c>
       <c r="C8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" t="s">
         <v>64</v>
-      </c>
-      <c r="E8" t="s">
-        <v>63</v>
-      </c>
-      <c r="F8" t="s">
-        <v>65</v>
       </c>
       <c r="G8">
         <v>55</v>
@@ -1075,13 +1075,13 @@
         <v>24</v>
       </c>
       <c r="C9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" t="s">
         <v>68</v>
       </c>
-      <c r="D9" t="s">
-        <v>69</v>
-      </c>
       <c r="E9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
@@ -1098,13 +1098,13 @@
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
@@ -1121,13 +1121,13 @@
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F12" t="s">
         <v>10</v>
@@ -1167,13 +1167,13 @@
         <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F13" t="s">
         <v>10</v>
@@ -1190,13 +1190,13 @@
         <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F14" t="s">
         <v>10</v>
@@ -1213,13 +1213,13 @@
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F15" t="s">
         <v>10</v>
@@ -1236,13 +1236,13 @@
         <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" t="s">
         <v>85</v>
-      </c>
-      <c r="F16" t="s">
-        <v>86</v>
       </c>
       <c r="G16">
         <v>56</v>
@@ -1256,13 +1256,13 @@
         <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" t="s">
         <v>87</v>
-      </c>
-      <c r="F17" t="s">
-        <v>88</v>
       </c>
       <c r="G17">
         <v>56</v>
@@ -1279,10 +1279,10 @@
         <v>46</v>
       </c>
       <c r="D18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" t="s">
         <v>89</v>
-      </c>
-      <c r="E18" t="s">
-        <v>90</v>
       </c>
       <c r="F18" t="s">
         <v>10</v>
@@ -1299,13 +1299,13 @@
         <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F19" t="s">
         <v>9</v>
@@ -1322,13 +1322,13 @@
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F20" t="s">
         <v>9</v>
@@ -1345,13 +1345,13 @@
         <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21" t="s">
         <v>95</v>
-      </c>
-      <c r="F21" t="s">
-        <v>96</v>
       </c>
       <c r="G21">
         <v>57</v>
@@ -1368,10 +1368,10 @@
         <v>46</v>
       </c>
       <c r="D22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>36</v>
@@ -1391,10 +1391,10 @@
         <v>46</v>
       </c>
       <c r="D23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>36</v>
@@ -1411,16 +1411,16 @@
         <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D24" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" t="s">
         <v>99</v>
       </c>
-      <c r="E24" t="s">
-        <v>100</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G24">
         <v>58</v>
@@ -1437,10 +1437,10 @@
         <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F25" t="s">
         <v>39</v>
@@ -1457,16 +1457,16 @@
         <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E26" t="s">
         <v>102</v>
       </c>
-      <c r="E26" t="s">
-        <v>103</v>
-      </c>
       <c r="F26" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G26">
         <v>58</v>
@@ -1480,16 +1480,16 @@
         <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E27" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G27">
         <v>58</v>
@@ -1503,13 +1503,13 @@
         <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D28" t="s">
+        <v>104</v>
+      </c>
+      <c r="E28" t="s">
         <v>105</v>
-      </c>
-      <c r="E28" t="s">
-        <v>106</v>
       </c>
       <c r="F28" t="s">
         <v>26</v>
@@ -1529,10 +1529,10 @@
         <v>46</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F29" t="s">
         <v>42</v>
@@ -1552,13 +1552,13 @@
         <v>46</v>
       </c>
       <c r="D30" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E30" t="s">
         <v>117</v>
       </c>
-      <c r="E30" t="s">
-        <v>118</v>
-      </c>
       <c r="F30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G30">
         <v>60</v>
@@ -1569,16 +1569,16 @@
         <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
       </c>
       <c r="D31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F31" t="s">
         <v>17</v>
@@ -1592,16 +1592,16 @@
         <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
       </c>
       <c r="D32" t="s">
+        <v>128</v>
+      </c>
+      <c r="E32" t="s">
         <v>129</v>
-      </c>
-      <c r="E32" t="s">
-        <v>130</v>
       </c>
       <c r="F32" t="s">
         <v>17</v>
@@ -1615,19 +1615,19 @@
         <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
       </c>
       <c r="D33" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E33" t="s">
         <v>131</v>
       </c>
-      <c r="E33" t="s">
-        <v>132</v>
-      </c>
       <c r="F33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G33">
         <v>61</v>
@@ -1638,16 +1638,16 @@
         <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C34" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E34" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F34" t="s">
         <v>8</v>
@@ -1661,16 +1661,16 @@
         <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D35" t="s">
+        <v>135</v>
+      </c>
+      <c r="E35" t="s">
         <v>136</v>
-      </c>
-      <c r="E35" t="s">
-        <v>137</v>
       </c>
       <c r="F35" t="s">
         <v>8</v>
@@ -1684,16 +1684,16 @@
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D36" t="s">
+        <v>137</v>
+      </c>
+      <c r="E36" t="s">
         <v>138</v>
-      </c>
-      <c r="E36" t="s">
-        <v>139</v>
       </c>
       <c r="F36" t="s">
         <v>18</v>
@@ -1707,16 +1707,16 @@
         <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D37" t="s">
+        <v>139</v>
+      </c>
+      <c r="E37" t="s">
         <v>140</v>
-      </c>
-      <c r="E37" t="s">
-        <v>141</v>
       </c>
       <c r="F37" t="s">
         <v>18</v>
@@ -1730,16 +1730,16 @@
         <v>7</v>
       </c>
       <c r="B38" t="s">
+        <v>141</v>
+      </c>
+      <c r="C38" t="s">
+        <v>55</v>
+      </c>
+      <c r="D38" t="s">
         <v>142</v>
       </c>
-      <c r="C38" t="s">
-        <v>56</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>143</v>
-      </c>
-      <c r="E38" t="s">
-        <v>144</v>
       </c>
       <c r="F38" t="s">
         <v>18</v>
@@ -1753,16 +1753,16 @@
         <v>7</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C39" t="s">
+        <v>63</v>
+      </c>
+      <c r="E39" t="s">
         <v>145</v>
       </c>
-      <c r="C39" t="s">
-        <v>64</v>
-      </c>
-      <c r="E39" t="s">
-        <v>146</v>
-      </c>
       <c r="F39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G39">
         <v>70</v>
@@ -1773,16 +1773,16 @@
         <v>7</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C40" t="s">
+        <v>67</v>
+      </c>
+      <c r="D40" t="s">
         <v>147</v>
       </c>
-      <c r="C40" t="s">
-        <v>68</v>
-      </c>
-      <c r="D40" t="s">
-        <v>148</v>
-      </c>
       <c r="E40" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F40" t="s">
         <v>9</v>
@@ -1833,13 +1833,13 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" t="s">
         <v>59</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>60</v>
-      </c>
-      <c r="E2" t="s">
-        <v>61</v>
       </c>
       <c r="G2">
         <v>55</v>
@@ -1853,13 +1853,13 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" t="s">
         <v>66</v>
-      </c>
-      <c r="E3" t="s">
-        <v>67</v>
       </c>
       <c r="G3">
         <v>55</v>
@@ -1873,16 +1873,16 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" t="s">
         <v>75</v>
       </c>
-      <c r="E4" t="s">
-        <v>76</v>
-      </c>
       <c r="F4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G4">
         <v>56</v>
@@ -1896,13 +1896,13 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" t="s">
         <v>107</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>108</v>
-      </c>
-      <c r="E5" t="s">
-        <v>109</v>
       </c>
       <c r="F5" t="s">
         <v>10</v>
@@ -1919,13 +1919,13 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" t="s">
         <v>110</v>
-      </c>
-      <c r="E6" t="s">
-        <v>111</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>17</v>
@@ -1942,13 +1942,13 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" t="s">
         <v>112</v>
-      </c>
-      <c r="E7" t="s">
-        <v>113</v>
       </c>
       <c r="G7">
         <v>59</v>
@@ -1962,13 +1962,13 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" t="s">
         <v>114</v>
-      </c>
-      <c r="E8" t="s">
-        <v>115</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>17</v>
@@ -1985,13 +1985,13 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
+        <v>132</v>
+      </c>
+      <c r="E9" t="s">
         <v>133</v>
-      </c>
-      <c r="E9" t="s">
-        <v>134</v>
       </c>
       <c r="G9">
         <v>68</v>

--- a/resource/groundTruths/architecture/CF_M09_ground_truth_architecture.xlsx
+++ b/resource/groundTruths/architecture/CF_M09_ground_truth_architecture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/architecture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{089907FA-E1ED-914C-94E9-71344290D693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454A5E31-09D9-DE46-9191-71FB8622E00C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37980" yWindow="1440" windowWidth="12520" windowHeight="16600" xr2:uid="{5C48AE06-3142-BB44-8E2A-9AD236D99D27}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{5C48AE06-3142-BB44-8E2A-9AD236D99D27}"/>
   </bookViews>
   <sheets>
     <sheet name="Architectural Units" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="156">
   <si>
     <t>Document ID</t>
   </si>
@@ -233,9 +233,6 @@
     <t>CF_M09_AU06, CF_M09_AU05</t>
   </si>
   <si>
-    <t>3-layer architecture</t>
-  </si>
-  <si>
     <t>To decouple the components of the client-server model, a three-tier architecture has been used.</t>
   </si>
   <si>
@@ -495,6 +492,18 @@
   </si>
   <si>
     <t>NestJS</t>
+  </si>
+  <si>
+    <t>Three Layers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communication between the two is carried out via the internet using the REST API model [30] and the HTTP communication protocol </t>
+  </si>
+  <si>
+    <t>CF_M09_AU40</t>
+  </si>
+  <si>
+    <t>HTTP</t>
   </si>
 </sst>
 </file>
@@ -886,7 +895,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8BB644F-E3FB-9344-8618-EE146D2A8012}">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="28" x14ac:dyDescent="0.2">
@@ -912,7 +921,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -932,7 +941,7 @@
         <v>48</v>
       </c>
       <c r="F2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G2">
         <v>9</v>
@@ -949,13 +958,13 @@
         <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E3" t="s">
         <v>48</v>
       </c>
       <c r="F3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G3">
         <v>9</v>
@@ -1075,13 +1084,13 @@
         <v>24</v>
       </c>
       <c r="C9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
         <v>67</v>
       </c>
-      <c r="D9" t="s">
-        <v>68</v>
-      </c>
       <c r="E9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
@@ -1098,13 +1107,13 @@
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
@@ -1121,13 +1130,13 @@
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
@@ -1147,10 +1156,10 @@
         <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F12" t="s">
         <v>10</v>
@@ -1170,10 +1179,10 @@
         <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F13" t="s">
         <v>10</v>
@@ -1193,10 +1202,10 @@
         <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F14" t="s">
         <v>10</v>
@@ -1216,10 +1225,10 @@
         <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F15" t="s">
         <v>10</v>
@@ -1239,10 +1248,10 @@
         <v>63</v>
       </c>
       <c r="E16" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" t="s">
         <v>84</v>
-      </c>
-      <c r="F16" t="s">
-        <v>85</v>
       </c>
       <c r="G16">
         <v>56</v>
@@ -1259,10 +1268,10 @@
         <v>63</v>
       </c>
       <c r="E17" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" t="s">
         <v>86</v>
-      </c>
-      <c r="F17" t="s">
-        <v>87</v>
       </c>
       <c r="G17">
         <v>56</v>
@@ -1279,10 +1288,10 @@
         <v>46</v>
       </c>
       <c r="D18" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" t="s">
         <v>88</v>
-      </c>
-      <c r="E18" t="s">
-        <v>89</v>
       </c>
       <c r="F18" t="s">
         <v>10</v>
@@ -1299,13 +1308,13 @@
         <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F19" t="s">
         <v>9</v>
@@ -1322,13 +1331,13 @@
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F20" t="s">
         <v>9</v>
@@ -1348,10 +1357,10 @@
         <v>63</v>
       </c>
       <c r="E21" t="s">
+        <v>93</v>
+      </c>
+      <c r="F21" t="s">
         <v>94</v>
-      </c>
-      <c r="F21" t="s">
-        <v>95</v>
       </c>
       <c r="G21">
         <v>57</v>
@@ -1368,10 +1377,10 @@
         <v>46</v>
       </c>
       <c r="D22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>36</v>
@@ -1391,10 +1400,10 @@
         <v>46</v>
       </c>
       <c r="D23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>36</v>
@@ -1414,13 +1423,13 @@
         <v>50</v>
       </c>
       <c r="D24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" t="s">
         <v>98</v>
       </c>
-      <c r="E24" t="s">
-        <v>99</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G24">
         <v>58</v>
@@ -1437,10 +1446,10 @@
         <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F25" t="s">
         <v>39</v>
@@ -1460,13 +1469,13 @@
         <v>50</v>
       </c>
       <c r="D26" t="s">
+        <v>100</v>
+      </c>
+      <c r="E26" t="s">
         <v>101</v>
       </c>
-      <c r="E26" t="s">
-        <v>102</v>
-      </c>
       <c r="F26" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G26">
         <v>58</v>
@@ -1483,13 +1492,13 @@
         <v>55</v>
       </c>
       <c r="D27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E27" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G27">
         <v>58</v>
@@ -1506,10 +1515,10 @@
         <v>50</v>
       </c>
       <c r="D28" t="s">
+        <v>103</v>
+      </c>
+      <c r="E28" t="s">
         <v>104</v>
-      </c>
-      <c r="E28" t="s">
-        <v>105</v>
       </c>
       <c r="F28" t="s">
         <v>26</v>
@@ -1529,10 +1538,10 @@
         <v>46</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F29" t="s">
         <v>42</v>
@@ -1552,13 +1561,13 @@
         <v>46</v>
       </c>
       <c r="D30" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E30" t="s">
         <v>116</v>
       </c>
-      <c r="E30" t="s">
-        <v>117</v>
-      </c>
       <c r="F30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G30">
         <v>60</v>
@@ -1569,16 +1578,16 @@
         <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
       </c>
       <c r="D31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F31" t="s">
         <v>17</v>
@@ -1592,16 +1601,16 @@
         <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
       </c>
       <c r="D32" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32" t="s">
         <v>128</v>
-      </c>
-      <c r="E32" t="s">
-        <v>129</v>
       </c>
       <c r="F32" t="s">
         <v>17</v>
@@ -1615,19 +1624,19 @@
         <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
       </c>
       <c r="D33" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E33" t="s">
         <v>130</v>
       </c>
-      <c r="E33" t="s">
-        <v>131</v>
-      </c>
       <c r="F33" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G33">
         <v>61</v>
@@ -1638,16 +1647,16 @@
         <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C34" t="s">
         <v>56</v>
       </c>
       <c r="D34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E34" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F34" t="s">
         <v>8</v>
@@ -1661,16 +1670,16 @@
         <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C35" t="s">
         <v>56</v>
       </c>
       <c r="D35" t="s">
+        <v>134</v>
+      </c>
+      <c r="E35" t="s">
         <v>135</v>
-      </c>
-      <c r="E35" t="s">
-        <v>136</v>
       </c>
       <c r="F35" t="s">
         <v>8</v>
@@ -1684,16 +1693,16 @@
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C36" t="s">
         <v>55</v>
       </c>
       <c r="D36" t="s">
+        <v>136</v>
+      </c>
+      <c r="E36" t="s">
         <v>137</v>
-      </c>
-      <c r="E36" t="s">
-        <v>138</v>
       </c>
       <c r="F36" t="s">
         <v>18</v>
@@ -1707,16 +1716,16 @@
         <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C37" t="s">
         <v>55</v>
       </c>
       <c r="D37" t="s">
+        <v>138</v>
+      </c>
+      <c r="E37" t="s">
         <v>139</v>
-      </c>
-      <c r="E37" t="s">
-        <v>140</v>
       </c>
       <c r="F37" t="s">
         <v>18</v>
@@ -1730,16 +1739,16 @@
         <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C38" t="s">
         <v>55</v>
       </c>
       <c r="D38" t="s">
+        <v>141</v>
+      </c>
+      <c r="E38" t="s">
         <v>142</v>
-      </c>
-      <c r="E38" t="s">
-        <v>143</v>
       </c>
       <c r="F38" t="s">
         <v>18</v>
@@ -1753,16 +1762,16 @@
         <v>7</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C39" t="s">
         <v>63</v>
       </c>
       <c r="E39" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G39">
         <v>70</v>
@@ -1773,22 +1782,42 @@
         <v>7</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C40" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" t="s">
         <v>146</v>
       </c>
-      <c r="C40" t="s">
-        <v>67</v>
-      </c>
-      <c r="D40" t="s">
-        <v>147</v>
-      </c>
       <c r="E40" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F40" t="s">
         <v>9</v>
       </c>
       <c r="G40">
         <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>154</v>
+      </c>
+      <c r="C41" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" t="s">
+        <v>155</v>
+      </c>
+      <c r="E41" t="s">
+        <v>153</v>
+      </c>
+      <c r="G41">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1856,10 +1885,10 @@
         <v>58</v>
       </c>
       <c r="D3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E3" t="s">
         <v>65</v>
-      </c>
-      <c r="E3" t="s">
-        <v>66</v>
       </c>
       <c r="G3">
         <v>55</v>
@@ -1876,13 +1905,13 @@
         <v>58</v>
       </c>
       <c r="D4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" t="s">
         <v>74</v>
       </c>
-      <c r="E4" t="s">
-        <v>75</v>
-      </c>
       <c r="F4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G4">
         <v>56</v>
@@ -1896,13 +1925,13 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" t="s">
         <v>106</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>107</v>
-      </c>
-      <c r="E5" t="s">
-        <v>108</v>
       </c>
       <c r="F5" t="s">
         <v>10</v>
@@ -1919,13 +1948,13 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" t="s">
         <v>109</v>
-      </c>
-      <c r="E6" t="s">
-        <v>110</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>17</v>
@@ -1942,13 +1971,13 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" t="s">
         <v>111</v>
-      </c>
-      <c r="E7" t="s">
-        <v>112</v>
       </c>
       <c r="G7">
         <v>59</v>
@@ -1962,13 +1991,13 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" t="s">
         <v>113</v>
-      </c>
-      <c r="E8" t="s">
-        <v>114</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>17</v>
@@ -1985,13 +2014,13 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" t="s">
         <v>132</v>
-      </c>
-      <c r="E9" t="s">
-        <v>133</v>
       </c>
       <c r="G9">
         <v>68</v>
